--- a/testcases/Summary_Report.xlsx
+++ b/testcases/Summary_Report.xlsx
@@ -507,13 +507,13 @@
         <v>400</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>32</v>
